--- a/public/assets/example-lead-format.xlsx
+++ b/public/assets/example-lead-format.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NithyanandamN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nithyanandham\projects\crm_nextjs_v1\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F1D284-EAAE-4D20-A41F-1190691F3208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF5BB5F-E3AD-46C3-913D-88EB19827731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="example-lead-format" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>customer_name</t>
   </si>
@@ -98,6 +98,18 @@
   </si>
   <si>
     <t>Test Remarks 3</t>
+  </si>
+  <si>
+    <t>user_email</t>
+  </si>
+  <si>
+    <t>girish@fullbasketproperty.com</t>
+  </si>
+  <si>
+    <t>ashwaq@fullbasketproperty.com</t>
+  </si>
+  <si>
+    <t>arbazkhan@fullbasketproperty.com</t>
   </si>
 </sst>
 </file>
@@ -373,19 +385,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -410,13 +422,16 @@
       <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>9944893484</v>
+        <v>9551295512</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -436,13 +451,16 @@
       <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1">
-        <v>1234567890</v>
+        <v>9551295513</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
@@ -462,13 +480,16 @@
       <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>1234567890</v>
+        <v>9551295514</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
@@ -487,6 +508,9 @@
       </c>
       <c r="H4" s="2" t="s">
         <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
